--- a/data/b2_indio/B2 Índio 03-2026.xlsx
+++ b/data/b2_indio/B2 Índio 03-2026.xlsx
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>392.46</v>
+        <v>379.07</v>
       </c>
     </row>
     <row r="3">
@@ -4873,34 +4873,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>971.5700000000001</v>
+        <v>2575.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1356.75</v>
+        <v>51144.7</v>
       </c>
     </row>
     <row r="5">
@@ -4909,124 +4909,124 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>52307.85</v>
+        <v>1696.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46089</v>
+        <v>46088</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3002.77</v>
+        <v>965.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46091</v>
+        <v>46089</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3900</v>
+        <v>3031.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2158.79</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2034.01</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46096</v>
+        <v>46093</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>10072.67</v>
+        <v>1124.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46096</v>
+        <v>46093</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1655.91</v>
+        <v>2169.24</v>
       </c>
     </row>
     <row r="12">
@@ -5035,52 +5035,52 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3241.24</v>
+        <v>9541.879999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2331.14</v>
+        <v>1724.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46098</v>
+        <v>46096</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1548.93</v>
+        <v>3067.74</v>
       </c>
     </row>
     <row r="15">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>18313.8</v>
+        <v>18295.37</v>
       </c>
     </row>
     <row r="16">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3153.88</v>
+        <v>3132.58</v>
       </c>
     </row>
     <row r="17">
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3402.18</v>
+        <v>3445.91</v>
       </c>
     </row>
     <row r="18">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>834.24</v>
+        <v>816.21</v>
       </c>
     </row>
   </sheetData>
